--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -978,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -1032,7 +1032,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -1055,7 +1055,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -1109,7 +1109,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -1132,7 +1132,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -1186,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1209,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1263,7 +1263,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1286,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1363,7 +1363,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1440,7 +1440,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1494,7 +1494,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1517,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1571,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1594,7 +1594,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -1648,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1671,7 +1671,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1725,7 +1725,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1748,7 +1748,7 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1802,7 +1802,7 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1879,7 +1879,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1902,7 +1902,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1956,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1979,7 +1979,7 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>7</v>
@@ -2033,7 +2033,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2056,7 +2056,7 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -2110,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2133,7 +2133,7 @@
         <v>9</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -2187,7 +2187,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2210,7 +2210,7 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2264,7 +2264,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2287,7 +2287,7 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2328,7 +2328,7 @@
         <v>10</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -2382,7 +2382,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2459,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2482,7 +2482,7 @@
         <v>9</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -2536,7 +2536,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2559,7 +2559,7 @@
         <v>9</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -2613,7 +2613,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2636,7 +2636,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2690,7 +2690,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2713,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>6</v>
@@ -2767,7 +2767,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2790,7 +2790,7 @@
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -2844,7 +2844,7 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2867,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>8</v>
@@ -2921,7 +2921,7 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2944,7 +2944,7 @@
         <v>8</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -2998,7 +2998,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>9</v>
@@ -3075,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3098,7 +3098,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <v>10</v>
@@ -3152,7 +3152,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3175,7 +3175,7 @@
         <v>6</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -3229,7 +3229,7 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3252,7 +3252,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -3306,7 +3306,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3329,7 +3329,7 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E35">
         <v>8</v>
@@ -3383,7 +3383,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3406,7 +3406,7 @@
         <v>9</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E36">
         <v>7</v>
@@ -3460,7 +3460,7 @@
         <v>9</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3593,7 +3593,7 @@
         <v>105.7</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>93.3</v>
@@ -3652,7 +3652,7 @@
         <v>105.7</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>60</v>
@@ -3711,7 +3711,7 @@
         <v>105.7</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -3770,7 +3770,7 @@
         <v>105.7</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3829,7 +3829,7 @@
         <v>105.7</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3888,7 +3888,7 @@
         <v>105.7</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3947,7 +3947,7 @@
         <v>105.7</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -4006,7 +4006,7 @@
         <v>105.7</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -4065,7 +4065,7 @@
         <v>105.7</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E12">
         <v>93.3</v>
@@ -4124,7 +4124,7 @@
         <v>105.7</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4183,7 +4183,7 @@
         <v>105.7</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4242,7 +4242,7 @@
         <v>105.7</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -4301,7 +4301,7 @@
         <v>105.7</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4360,7 +4360,7 @@
         <v>105.7</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -4419,7 +4419,7 @@
         <v>105.7</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -4478,7 +4478,7 @@
         <v>105.7</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -4537,7 +4537,7 @@
         <v>105.7</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -4596,7 +4596,7 @@
         <v>105.7</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -4628,7 +4628,7 @@
         <v>105.7</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -4687,7 +4687,7 @@
         <v>105.7</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -4746,7 +4746,7 @@
         <v>105.7</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -4805,7 +4805,7 @@
         <v>105.7</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -4864,7 +4864,7 @@
         <v>105.7</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4923,7 +4923,7 @@
         <v>105.7</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -4982,7 +4982,7 @@
         <v>105.7</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -5041,7 +5041,7 @@
         <v>105.7</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -5100,7 +5100,7 @@
         <v>105.7</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -5159,7 +5159,7 @@
         <v>105.7</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -5218,7 +5218,7 @@
         <v>105.7</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -5277,7 +5277,7 @@
         <v>105.7</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -5336,7 +5336,7 @@
         <v>105.7</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -5395,7 +5395,7 @@
         <v>105.7</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -5454,7 +5454,7 @@
         <v>105.7</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E36">
         <v>100</v>
@@ -5563,22 +5563,25 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5748,7 +5751,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5773,666 +5776,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920392</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920205</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22321052600528</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920362</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920207</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920393</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920420</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920210</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920394</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920211</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920423</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920213</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920374</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920214</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920215</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20322051180081</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920216</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920218</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920217</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920219</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920220</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920221</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920222</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920223</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920421</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920224</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920225</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920226</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920365</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920228</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920227</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920229</v>
-      </c>
-      <c r="B34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6480,7 +5823,7 @@
         <v>123</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6497,7 +5840,7 @@
         <v>124</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6514,7 +5857,7 @@
         <v>125</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6531,7 +5874,7 @@
         <v>126</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6548,7 +5891,7 @@
         <v>127</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6565,7 +5908,7 @@
         <v>128</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6582,7 +5925,7 @@
         <v>129</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6599,7 +5942,7 @@
         <v>130</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6616,7 +5959,7 @@
         <v>131</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6633,7 +5976,7 @@
         <v>132</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6650,7 +5993,7 @@
         <v>133</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6667,7 +6010,7 @@
         <v>134</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6684,7 +6027,7 @@
         <v>135</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6701,7 +6044,7 @@
         <v>136</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6718,7 +6061,7 @@
         <v>137</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6735,7 +6078,7 @@
         <v>138</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6752,7 +6095,7 @@
         <v>139</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6769,7 +6112,7 @@
         <v>140</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6786,7 +6129,7 @@
         <v>141</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6803,7 +6146,7 @@
         <v>142</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6820,7 +6163,7 @@
         <v>143</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6837,7 +6180,7 @@
         <v>144</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6854,7 +6197,7 @@
         <v>145</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6871,7 +6214,7 @@
         <v>146</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6888,7 +6231,7 @@
         <v>147</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6905,7 +6248,7 @@
         <v>148</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6922,7 +6265,7 @@
         <v>149</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6939,7 +6282,7 @@
         <v>150</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6956,7 +6299,7 @@
         <v>151</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6973,7 +6316,7 @@
         <v>152</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6990,7 +6333,7 @@
         <v>153</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7007,7 +6350,7 @@
         <v>154</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7024,7 +6367,7 @@
         <v>155</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7034,7 +6377,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7107,7 +6450,7 @@
         <v>57</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7130,7 +6473,7 @@
         <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7176,21 +6519,21 @@
         <v>57</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920392</v>
+        <v>22330051920205</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -7199,21 +6542,21 @@
         <v>57</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920205</v>
+        <v>22330051920423</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -7222,21 +6565,21 @@
         <v>57</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920207</v>
+        <v>22330051920374</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -7245,21 +6588,21 @@
         <v>57</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920393</v>
+        <v>22330051920222</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -7268,513 +6611,7 @@
         <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920420</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920211</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920423</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920374</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920214</v>
-      </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920215</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20322051180081</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920216</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920218</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920217</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>142</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920219</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920220</v>
-      </c>
-      <c r="B22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920221</v>
-      </c>
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920222</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920223</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920421</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920224</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920225</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920226</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920228</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920227</v>
-      </c>
-      <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" t="s">
-        <v>154</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920229</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -201,7 +201,7 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
     <t>Camacho Juárez Sergio Eduardo</t>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -132,6 +131,9 @@
     <t>RAMOS VILLEGAS NATALIA</t>
   </si>
   <si>
+    <t>RIVERA HERNANDEZ KEVIN RAUL</t>
+  </si>
+  <si>
     <t>RONZON VELAZQUEZ ARAWY</t>
   </si>
   <si>
@@ -222,277 +224,82 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>KEVIN RAUL</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>USCANGA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
   </si>
   <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
     <t>CADENA</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>JORGE</t>
   </si>
   <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MERLIN</t>
-  </si>
-  <si>
-    <t>MONTES</t>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>EMILIANO GERARDO</t>
   </si>
   <si>
-    <t>ASHLEY</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>SAIRA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ELIDA CITLALI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
-  </si>
-  <si>
     <t>DANA PAOLA</t>
   </si>
   <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
     <t>KARLA YARITZY</t>
   </si>
   <si>
-    <t>ROSARIO DE JESUS</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>ALAN SANTIAGO</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>DEMY</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
     <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>AMERICA</t>
-  </si>
-  <si>
-    <t>EMILIANO DE JESUS</t>
-  </si>
-  <si>
-    <t>ANDREA JANETH</t>
-  </si>
-  <si>
-    <t>ESTRELLA SARAHI</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -545,11 +352,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -990,7 +798,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1067,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1144,7 +952,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1180,7 +988,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1221,7 +1029,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1298,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1334,7 +1142,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1375,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1452,7 +1260,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1529,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1565,7 +1373,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1606,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1683,7 +1491,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1760,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1837,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1873,7 +1681,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1914,7 +1722,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1991,7 +1799,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2027,7 +1835,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2068,7 +1876,7 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2145,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2181,7 +1989,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>9</v>
@@ -2222,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2290,7 +2098,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2308,7 +2116,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2340,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2417,7 +2225,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2494,7 +2302,7 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2530,7 +2338,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2571,7 +2379,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2607,7 +2415,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>9</v>
@@ -2648,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2725,7 +2533,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2802,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2864,22 +2672,22 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2915,22 +2723,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2938,7 +2746,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>8</v>
@@ -2950,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -2992,7 +2800,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3004,10 +2812,10 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3015,25 +2823,25 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>8</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3069,22 +2877,22 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>8</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3095,22 +2903,22 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32">
         <v>10</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3149,19 +2957,19 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3169,25 +2977,25 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3223,22 +3031,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3246,25 +3054,25 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3300,22 +3108,22 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3335,13 +3143,13 @@
         <v>8</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3377,7 +3185,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3389,10 +3197,10 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3406,19 +3214,19 @@
         <v>9</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3460,15 +3268,92 @@
         <v>9</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+      <c r="E37">
+        <v>7</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>9</v>
+      </c>
+      <c r="H37">
+        <v>9</v>
+      </c>
+      <c r="I37">
+        <v>-1</v>
+      </c>
+      <c r="J37">
+        <v>-1</v>
+      </c>
+      <c r="K37">
+        <v>-1</v>
+      </c>
+      <c r="L37">
+        <v>-1</v>
+      </c>
+      <c r="M37">
+        <v>-1</v>
+      </c>
+      <c r="N37">
+        <v>-1</v>
+      </c>
+      <c r="O37">
+        <v>-1</v>
+      </c>
+      <c r="P37">
+        <v>-1</v>
+      </c>
+      <c r="Q37">
+        <v>-1</v>
+      </c>
+      <c r="R37">
+        <v>-1</v>
+      </c>
+      <c r="S37">
+        <v>-1</v>
+      </c>
+      <c r="T37">
+        <v>10</v>
+      </c>
+      <c r="U37">
+        <v>9</v>
+      </c>
+      <c r="V37">
+        <v>8</v>
+      </c>
+      <c r="W37">
+        <v>7</v>
+      </c>
+      <c r="X37">
+        <v>10</v>
+      </c>
+      <c r="Y37">
         <v>9</v>
       </c>
     </row>
@@ -3485,7 +3370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3494,7 +3379,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3502,7 +3387,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -3510,7 +3395,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -3605,7 +3490,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3664,7 +3549,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3723,7 +3608,7 @@
         <v>95</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3782,7 +3667,7 @@
         <v>85</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3841,7 +3726,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3900,7 +3785,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3959,7 +3844,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4018,7 +3903,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4077,7 +3962,7 @@
         <v>90</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4136,7 +4021,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4195,7 +4080,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4254,7 +4139,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4313,7 +4198,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4372,7 +4257,7 @@
         <v>95</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4431,7 +4316,7 @@
         <v>90</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4490,7 +4375,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4549,7 +4434,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4599,7 +4484,7 @@
         <v>110</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4640,7 +4525,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4699,7 +4584,7 @@
         <v>95</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4758,7 +4643,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4817,7 +4702,7 @@
         <v>95</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4876,7 +4761,7 @@
         <v>95</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4935,7 +4820,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4994,7 +4879,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5038,22 +4923,22 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>105.7</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5100,19 +4985,19 @@
         <v>105.7</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E30">
         <v>100</v>
       </c>
       <c r="F30">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5159,19 +5044,19 @@
         <v>105.7</v>
       </c>
       <c r="D31">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G31">
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5218,7 +5103,7 @@
         <v>105.7</v>
       </c>
       <c r="D32">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -5230,7 +5115,7 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5271,25 +5156,25 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>105.7</v>
       </c>
       <c r="D33">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E33">
         <v>100</v>
       </c>
       <c r="F33">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G33">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5330,7 +5215,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C34">
         <v>105.7</v>
@@ -5342,13 +5227,13 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G34">
         <v>95</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5395,7 +5280,7 @@
         <v>105.7</v>
       </c>
       <c r="D35">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -5404,10 +5289,10 @@
         <v>100</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5466,7 +5351,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5499,6 +5384,65 @@
         <v>0</v>
       </c>
       <c r="S36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37">
+        <v>100</v>
+      </c>
+      <c r="C37">
+        <v>105.7</v>
+      </c>
+      <c r="D37">
+        <v>110</v>
+      </c>
+      <c r="E37">
+        <v>100</v>
+      </c>
+      <c r="F37">
+        <v>100</v>
+      </c>
+      <c r="G37">
+        <v>100</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>0</v>
       </c>
     </row>
@@ -5518,6 +5462,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5525,31 +5471,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5557,10 +5503,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>22</v>
@@ -5568,20 +5514,20 @@
       <c r="E2">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>66.67</v>
-      </c>
-      <c r="G2">
-        <v>33.33</v>
+      <c r="F2" s="2">
+        <v>64.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>32.4</v>
       </c>
       <c r="H2">
         <v>6.9</v>
       </c>
       <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2.9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5589,10 +5535,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>28</v>
@@ -5600,20 +5546,20 @@
       <c r="E3">
         <v>4</v>
       </c>
-      <c r="F3">
-        <v>87.5</v>
-      </c>
-      <c r="G3">
-        <v>12.5</v>
+      <c r="F3" s="2">
+        <v>84.8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>12.1</v>
       </c>
       <c r="H3">
         <v>7.3</v>
       </c>
       <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5621,10 +5567,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -5632,20 +5578,20 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4">
-        <v>87.5</v>
-      </c>
-      <c r="G4">
-        <v>12.5</v>
+      <c r="F4" s="2">
+        <v>84.8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>12.1</v>
       </c>
       <c r="H4">
         <v>7.6</v>
       </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5653,30 +5599,30 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5">
-        <v>87.88</v>
-      </c>
-      <c r="G5">
-        <v>12.12</v>
+      <c r="F5" s="2">
+        <v>88.2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>11.8</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5685,10 +5631,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -5696,20 +5642,20 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>90.91</v>
-      </c>
-      <c r="G6">
-        <v>9.09</v>
+      <c r="F6" s="2">
+        <v>88.2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
         <v>7.9</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2.9</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5717,10 +5663,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>31</v>
@@ -5728,20 +5674,20 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>96.88</v>
-      </c>
-      <c r="G7">
-        <v>3.13</v>
+      <c r="F7" s="2">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
       </c>
       <c r="H7">
         <v>7.3</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5751,7 +5697,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5760,22 +5706,122 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>22330051920425</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>22330051920425</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>22330051920425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>22330051920425</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>22330051920425</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5784,598 +5830,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920392</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920205</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22321052600528</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920362</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920207</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920393</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920420</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920210</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920394</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920211</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920423</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920213</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920374</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920214</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920215</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20322051180081</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920216</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920218</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920217</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920219</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920220</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920221</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920222</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920223</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920421</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920224</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920225</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920226</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920365</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920228</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920227</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920229</v>
-      </c>
-      <c r="B34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6386,22 +5840,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6412,19 +5866,19 @@
         <v>22330051920362</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6435,19 +5889,19 @@
         <v>22330051920362</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6458,19 +5912,19 @@
         <v>22330051920394</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6481,19 +5935,19 @@
         <v>22330051920394</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6504,19 +5958,19 @@
         <v>21330051920002</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6527,19 +5981,19 @@
         <v>22330051920205</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6550,19 +6004,19 @@
         <v>22330051920423</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6573,19 +6027,19 @@
         <v>22330051920374</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6596,19 +6050,19 @@
         <v>22330051920222</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -233,64 +233,64 @@
     <t>KEVIN RAUL</t>
   </si>
   <si>
-    <t>ALFONSO</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>VALLEJO</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>CADENA</t>
   </si>
   <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
     <t>DANA PAOLA</t>
   </si>
   <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
+    <t>MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -801,19 +801,19 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -837,7 +837,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -849,7 +849,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -878,19 +878,19 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -914,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -926,7 +926,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -955,19 +955,19 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1032,19 +1032,19 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1068,7 +1068,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1109,19 +1109,19 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1151,7 +1151,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1186,19 +1186,19 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1222,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1234,7 +1234,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1263,19 +1263,19 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1299,19 +1299,19 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1352,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1388,7 +1388,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1417,19 +1417,19 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1459,7 +1459,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1494,19 +1494,19 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1530,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1542,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1571,19 +1571,19 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1607,13 +1607,13 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1648,19 +1648,19 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1690,7 +1690,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1725,19 +1725,19 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1802,19 +1802,19 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1838,19 +1838,19 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1879,19 +1879,19 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1915,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -1956,19 +1956,19 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1992,19 +1992,19 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2033,19 +2033,19 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2069,13 +2069,13 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2101,7 +2101,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2119,7 +2119,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2151,19 +2151,19 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2193,7 +2193,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2228,19 +2228,19 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2264,19 +2264,19 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>6</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2305,19 +2305,19 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2353,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2382,19 +2382,19 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2430,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2459,19 +2459,19 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2495,13 +2495,13 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2536,19 +2536,19 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2578,13 +2578,13 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2613,19 +2613,19 @@
         <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2655,7 +2655,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2672,37 +2672,37 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>-1</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H29">
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2726,19 +2726,19 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>-1</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2767,19 +2767,19 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2803,19 +2803,19 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>6</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2844,19 +2844,19 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2892,7 +2892,7 @@
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2921,19 +2921,19 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2969,7 +2969,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2998,19 +2998,19 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3034,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3075,19 +3075,19 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3111,7 +3111,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3123,7 +3123,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3152,19 +3152,19 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3188,7 +3188,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3200,7 +3200,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3229,19 +3229,19 @@
         <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3265,13 +3265,13 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>9</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -3306,19 +3306,19 @@
         <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3348,7 +3348,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3493,19 +3493,19 @@
         <v>96</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3552,19 +3552,19 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3611,19 +3611,19 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3670,19 +3670,19 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3729,19 +3729,19 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3788,19 +3788,19 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3847,19 +3847,19 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3965,19 +3965,19 @@
         <v>96</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4024,19 +4024,19 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4083,19 +4083,19 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4142,19 +4142,19 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4201,19 +4201,19 @@
         <v>96</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4260,19 +4260,19 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4319,19 +4319,19 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4378,19 +4378,19 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4437,19 +4437,19 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4528,19 +4528,19 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4587,19 +4587,19 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4646,19 +4646,19 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4705,19 +4705,19 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4764,19 +4764,19 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4823,19 +4823,19 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4882,19 +4882,19 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4923,37 +4923,37 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5000,19 +5000,19 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5059,19 +5059,19 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5118,19 +5118,19 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5177,19 +5177,19 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5236,19 +5236,19 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5295,19 +5295,19 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5354,19 +5354,19 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5413,19 +5413,19 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>105.7</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5541,30 +5541,30 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>84.8</v>
+        <v>78.8</v>
       </c>
       <c r="G3" s="2">
-        <v>12.1</v>
+        <v>21.2</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5585,7 +5585,7 @@
         <v>12.1</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -5640,22 +5640,22 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
         <v>88.2</v>
       </c>
       <c r="G6" s="2">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5669,25 +5669,25 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5697,7 +5697,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5741,7 +5741,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5758,70 +5758,10 @@
         <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920425</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920425</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920425</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5831,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5863,7 +5803,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>22330051920374</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -5875,10 +5815,10 @@
         <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5886,7 +5826,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920362</v>
+        <v>22330051920374</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -5898,10 +5838,10 @@
         <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5909,7 +5849,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920394</v>
+        <v>22330051920222</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
@@ -5932,7 +5872,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920394</v>
+        <v>22330051920222</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
@@ -5947,7 +5887,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5955,16 +5895,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920002</v>
+        <v>22330051920425</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5973,44 +5913,44 @@
         <v>58</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920205</v>
+        <v>22330051920425</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920423</v>
+        <v>21330051920002</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6024,16 +5964,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920374</v>
+        <v>22330051920205</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -6047,16 +5987,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920222</v>
+        <v>22330051920394</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6065,6 +6005,52 @@
         <v>58</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920423</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920224</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -224,70 +224,61 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>KEVIN RAUL</t>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>SILVESTRE</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>JORGE</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
     <t>OLIVARES</t>
   </si>
   <si>
+    <t>ASHLEY</t>
+  </si>
+  <si>
     <t>KARLA YARITZY</t>
   </si>
   <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
     <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
   </si>
   <si>
     <t>MICHELLE</t>
@@ -804,13 +795,13 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -846,7 +837,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -881,13 +872,13 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -958,13 +949,13 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1000,7 +991,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1035,13 +1026,13 @@
         <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1077,7 +1068,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1112,13 +1103,13 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1148,13 +1139,13 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>7</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1189,13 +1180,13 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1266,13 +1257,13 @@
         <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1302,13 +1293,13 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1343,13 +1334,13 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1379,13 +1370,13 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1420,13 +1411,13 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1497,13 +1488,13 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -1539,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1574,13 +1565,13 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1616,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1651,13 +1642,13 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>6</v>
@@ -1687,7 +1678,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1728,13 +1719,13 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1805,13 +1796,13 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -1847,7 +1838,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1882,13 +1873,13 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -1959,13 +1950,13 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -2001,7 +1992,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2036,13 +2027,13 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>8</v>
@@ -2072,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2104,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2154,13 +2145,13 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -2231,13 +2222,13 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -2267,13 +2258,13 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2308,13 +2299,13 @@
         <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2344,7 +2335,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2385,13 +2376,13 @@
         <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2462,13 +2453,13 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>7</v>
@@ -2498,13 +2489,13 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2539,13 +2530,13 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2575,7 +2566,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2616,13 +2607,13 @@
         <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>9</v>
@@ -2658,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2675,13 +2666,13 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>9</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -2693,13 +2684,13 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2729,13 +2720,13 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2770,13 +2761,13 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -2806,7 +2797,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -2847,13 +2838,13 @@
         <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>5</v>
@@ -2883,13 +2874,13 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -2924,13 +2915,13 @@
         <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -2960,7 +2951,7 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3001,13 +2992,13 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3037,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3078,13 +3069,13 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3114,7 +3105,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3155,13 +3146,13 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -3232,13 +3223,13 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3309,13 +3300,13 @@
         <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>9</v>
@@ -3496,13 +3487,13 @@
         <v>105.7</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -3555,13 +3546,13 @@
         <v>105.7</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -3614,13 +3605,13 @@
         <v>105.7</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M6">
         <v>95</v>
@@ -3673,13 +3664,13 @@
         <v>105.7</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3732,13 +3723,13 @@
         <v>105.7</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -3791,13 +3782,13 @@
         <v>105.7</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3850,13 +3841,13 @@
         <v>105.7</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3909,13 +3900,13 @@
         <v>105.7</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3968,13 +3959,13 @@
         <v>105.7</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4027,13 +4018,13 @@
         <v>105.7</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -4086,13 +4077,13 @@
         <v>105.7</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -4145,13 +4136,13 @@
         <v>105.7</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -4204,13 +4195,13 @@
         <v>105.7</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -4263,13 +4254,13 @@
         <v>105.7</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -4322,13 +4313,13 @@
         <v>105.7</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -4381,13 +4372,13 @@
         <v>105.7</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -4440,13 +4431,13 @@
         <v>105.7</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -4490,7 +4481,7 @@
         <v>105.7</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4531,13 +4522,13 @@
         <v>105.7</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -4590,13 +4581,13 @@
         <v>105.7</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4649,13 +4640,13 @@
         <v>105.7</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -4708,13 +4699,13 @@
         <v>105.7</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4767,13 +4758,13 @@
         <v>105.7</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -4826,13 +4817,13 @@
         <v>105.7</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -4885,13 +4876,13 @@
         <v>105.7</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -4926,13 +4917,13 @@
         <v>105.7</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -4944,13 +4935,13 @@
         <v>105.7</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5003,13 +4994,13 @@
         <v>105.7</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -5062,13 +5053,13 @@
         <v>105.7</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -5121,13 +5112,13 @@
         <v>105.7</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -5180,13 +5171,13 @@
         <v>105.7</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -5239,13 +5230,13 @@
         <v>105.7</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -5298,13 +5289,13 @@
         <v>105.7</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -5357,13 +5348,13 @@
         <v>105.7</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -5416,13 +5407,13 @@
         <v>105.7</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -5509,25 +5500,25 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>64.7</v>
+        <v>76.5</v>
       </c>
       <c r="G2" s="2">
-        <v>32.4</v>
+        <v>23.5</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5573,25 +5564,25 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4" s="2">
         <v>12.1</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5697,7 +5688,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5724,46 +5715,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920425</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920425</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5771,7 +5722,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5803,16 +5754,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920374</v>
+        <v>22321052600528</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5826,16 +5777,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920374</v>
+        <v>22321052600528</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5849,16 +5800,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920222</v>
+        <v>22330051920374</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5872,16 +5823,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920222</v>
+        <v>22330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5895,16 +5846,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920425</v>
+        <v>21330051920002</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5913,44 +5864,44 @@
         <v>58</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920425</v>
+        <v>22330051920205</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920002</v>
+        <v>22330051920394</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5964,22 +5915,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920205</v>
+        <v>22330051920222</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5987,70 +5938,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920394</v>
+        <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920423</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920224</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -1337,7 +1337,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -3903,7 +3903,7 @@
         <v>110</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -3466,10 +3466,10 @@
         <v>90</v>
       </c>
       <c r="C4">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="E4">
         <v>93.3</v>
@@ -3481,40 +3481,40 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I4">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>105</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3525,10 +3525,10 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>60</v>
@@ -3543,37 +3543,37 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J5">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="K5">
         <v>80</v>
       </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
       <c r="L5">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3584,10 +3584,10 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -3602,37 +3602,37 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M6">
         <v>95</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3643,10 +3643,10 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3661,37 +3661,37 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>105</v>
+        <v>79.5</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3702,10 +3702,10 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3720,37 +3720,37 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>110</v>
+        <v>93.2</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3761,10 +3761,10 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3779,37 +3779,37 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3820,10 +3820,10 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -3838,37 +3838,37 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3879,10 +3879,10 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -3897,10 +3897,10 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3912,22 +3912,22 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3938,10 +3938,10 @@
         <v>90</v>
       </c>
       <c r="C12">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D12">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="E12">
         <v>93.3</v>
@@ -3953,40 +3953,40 @@
         <v>90</v>
       </c>
       <c r="H12">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I12">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>90</v>
+        <v>72.7</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L12">
-        <v>20</v>
+        <v>47.5</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3997,10 +3997,10 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D13">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4015,10 +4015,10 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4030,22 +4030,22 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4056,10 +4056,10 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4074,37 +4074,37 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4115,10 +4115,10 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D15">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -4133,37 +4133,37 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>85</v>
+        <v>79.5</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4174,10 +4174,10 @@
         <v>90</v>
       </c>
       <c r="C16">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D16">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4189,13 +4189,13 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I16">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4207,22 +4207,22 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4233,10 +4233,10 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -4251,10 +4251,10 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -4263,25 +4263,25 @@
         <v>85</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4292,10 +4292,10 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -4310,10 +4310,10 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4322,25 +4322,25 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4351,10 +4351,10 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -4369,37 +4369,37 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4410,10 +4410,10 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -4428,37 +4428,37 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J20">
+        <v>93.2</v>
+      </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>95</v>
       </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4469,28 +4469,28 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4501,10 +4501,10 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -4519,10 +4519,10 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4534,22 +4534,22 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4560,10 +4560,10 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D23">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -4578,37 +4578,37 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4619,10 +4619,10 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -4637,10 +4637,10 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4652,22 +4652,22 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4678,10 +4678,10 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -4696,37 +4696,37 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4737,10 +4737,10 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4755,10 +4755,10 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4767,25 +4767,25 @@
         <v>95</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4796,10 +4796,10 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D27">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -4814,37 +4814,37 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>105</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="M27">
         <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4855,10 +4855,10 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -4873,37 +4873,37 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M28">
         <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4914,10 +4914,10 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -4932,10 +4932,10 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>105</v>
+        <v>93.2</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4947,22 +4947,22 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4973,10 +4973,10 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D30">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -4991,10 +4991,10 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -5006,22 +5006,22 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5032,10 +5032,10 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -5050,37 +5050,37 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>105</v>
+        <v>93.2</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M31">
         <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5091,10 +5091,10 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D32">
-        <v>105</v>
+        <v>95.5</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -5109,10 +5109,10 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>110</v>
+        <v>97.7</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5124,22 +5124,22 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5150,10 +5150,10 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -5168,10 +5168,10 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5183,22 +5183,22 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5209,10 +5209,10 @@
         <v>90</v>
       </c>
       <c r="C34">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D34">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -5224,40 +5224,40 @@
         <v>95</v>
       </c>
       <c r="H34">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I34">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>110</v>
+        <v>93.2</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5268,10 +5268,10 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D35">
-        <v>95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -5286,37 +5286,37 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5327,10 +5327,10 @@
         <v>100</v>
       </c>
       <c r="C36">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D36">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>100</v>
@@ -5345,37 +5345,37 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J36">
-        <v>105</v>
+        <v>97.7</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M36">
         <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5386,10 +5386,10 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="D37">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>100</v>
@@ -5404,10 +5404,10 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -5419,22 +5419,22 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -807,10 +807,10 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -819,7 +819,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -884,10 +884,10 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -896,7 +896,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -905,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -961,10 +961,10 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -973,7 +973,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -982,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1038,10 +1038,10 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1050,7 +1050,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1115,10 +1115,10 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1127,16 +1127,16 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1192,10 +1192,10 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1204,7 +1204,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1269,10 +1269,10 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1281,7 +1281,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1346,10 +1346,10 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1358,7 +1358,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1423,10 +1423,10 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1435,7 +1435,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1512,7 +1512,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1530,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1577,10 +1577,10 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1589,7 +1589,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1654,10 +1654,10 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1666,7 +1666,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1731,10 +1731,10 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1743,7 +1743,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1808,10 +1808,10 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1820,7 +1820,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1885,10 +1885,10 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1897,7 +1897,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -1915,7 +1915,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -1962,10 +1962,10 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -1974,7 +1974,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -1992,7 +1992,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2039,10 +2039,10 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2051,7 +2051,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2060,7 +2060,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2098,10 +2098,10 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2157,10 +2157,10 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2169,7 +2169,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2187,7 +2187,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2234,10 +2234,10 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2246,7 +2246,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2255,7 +2255,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2311,10 +2311,10 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2323,7 +2323,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2388,10 +2388,10 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2400,7 +2400,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2465,10 +2465,10 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2477,7 +2477,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2542,10 +2542,10 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2554,7 +2554,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2619,10 +2619,10 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2631,7 +2631,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2696,10 +2696,10 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2708,7 +2708,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2717,7 +2717,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -2773,10 +2773,10 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2785,7 +2785,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2794,7 +2794,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -2850,10 +2850,10 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -2862,7 +2862,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -2880,7 +2880,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -2927,10 +2927,10 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -2939,7 +2939,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -2948,7 +2948,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3004,10 +3004,10 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3016,7 +3016,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3081,10 +3081,10 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3093,7 +3093,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3158,10 +3158,10 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3170,7 +3170,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3179,7 +3179,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3235,10 +3235,10 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3247,7 +3247,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3256,7 +3256,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3312,10 +3312,10 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3324,7 +3324,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3499,7 +3499,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>93</v>
+        <v>86.3</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3511,7 +3511,7 @@
         <v>96.7</v>
       </c>
       <c r="R4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3570,7 +3570,7 @@
         <v>80</v>
       </c>
       <c r="R5">
-        <v>87.5</v>
+        <v>88.3</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3688,7 +3688,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>80</v>
+        <v>81.7</v>
       </c>
       <c r="S7">
         <v>92.5</v>
@@ -3747,7 +3747,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3806,7 +3806,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3865,7 +3865,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3924,7 +3924,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3971,7 +3971,7 @@
         <v>95</v>
       </c>
       <c r="N12">
-        <v>93</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3983,7 +3983,7 @@
         <v>96.7</v>
       </c>
       <c r="R12">
-        <v>47.5</v>
+        <v>58.3</v>
       </c>
       <c r="S12">
         <v>95</v>
@@ -4101,7 +4101,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4160,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>87.5</v>
+        <v>86.7</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4207,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>93</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4219,7 +4219,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>75</v>
+        <v>73.3</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4278,7 +4278,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="S17">
         <v>97.5</v>
@@ -4337,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S18">
         <v>95</v>
@@ -4396,7 +4396,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4455,7 +4455,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -4605,7 +4605,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>87.5</v>
+        <v>88.3</v>
       </c>
       <c r="S23">
         <v>97.5</v>
@@ -4723,7 +4723,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="S25">
         <v>97.5</v>
@@ -4782,7 +4782,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="S26">
         <v>97.5</v>
@@ -4841,7 +4841,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>82.5</v>
+        <v>81.7</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -4900,7 +4900,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -4959,7 +4959,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5077,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5242,7 +5242,7 @@
         <v>97.5</v>
       </c>
       <c r="N34">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5254,7 +5254,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>72.5</v>
+        <v>71.7</v>
       </c>
       <c r="S34">
         <v>97.5</v>
@@ -5372,7 +5372,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -5576,7 +5576,7 @@
         <v>12.1</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -816,7 +816,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -893,7 +893,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>6</v>
@@ -970,7 +970,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -1124,7 +1124,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>7</v>
@@ -1201,7 +1201,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>8</v>
@@ -1278,7 +1278,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1373,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1432,7 +1432,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -1509,7 +1509,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -1586,7 +1586,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -1663,7 +1663,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -1740,7 +1740,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>5</v>
@@ -1817,7 +1817,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1894,7 +1894,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -1971,7 +1971,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -2048,7 +2048,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2066,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2166,7 +2166,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2243,7 +2243,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -2320,7 +2320,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2397,7 +2397,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>6</v>
@@ -2474,7 +2474,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -2551,7 +2551,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>6</v>
@@ -2628,7 +2628,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -2705,7 +2705,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -2723,7 +2723,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2782,7 +2782,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -2936,7 +2936,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3013,7 +3013,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -3090,7 +3090,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>5</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -3244,7 +3244,7 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -3321,7 +3321,7 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="R4">
         <v>75</v>
@@ -3567,7 +3567,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="R5">
         <v>88.3</v>
@@ -3980,7 +3980,7 @@
         <v>72.7</v>
       </c>
       <c r="Q12">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="R12">
         <v>58.3</v>
@@ -5672,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -224,64 +224,46 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>MEDINA</t>
   </si>
   <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>JORGE</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>ASHLEY</t>
   </si>
   <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
     <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -822,7 +804,7 @@
         <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -840,7 +822,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -899,7 +881,7 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -976,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -994,7 +976,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1053,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1071,7 +1053,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1130,7 +1112,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1207,7 +1189,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1284,7 +1266,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1361,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1438,7 +1420,7 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1456,7 +1438,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1515,7 +1497,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1592,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1669,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1687,7 +1669,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1746,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1764,7 +1746,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1823,7 +1805,7 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1841,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1900,7 +1882,7 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1918,7 +1900,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1977,7 +1959,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -1995,7 +1977,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2054,7 +2036,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2172,7 +2154,7 @@
         <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2249,7 +2231,7 @@
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2326,7 +2308,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2403,7 +2385,7 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2421,7 +2403,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2480,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2557,7 +2539,7 @@
         <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2575,7 +2557,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2634,7 +2616,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2711,7 +2693,7 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2729,7 +2711,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2788,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -2865,7 +2847,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>8</v>
@@ -2883,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2942,7 +2924,7 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3019,7 +3001,7 @@
         <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3096,7 +3078,7 @@
         <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
         <v>5</v>
@@ -3173,7 +3155,7 @@
         <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3250,7 +3232,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3327,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3632,7 +3614,7 @@
         <v>90</v>
       </c>
       <c r="S6">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3691,7 +3673,7 @@
         <v>81.7</v>
       </c>
       <c r="S7">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3986,7 +3968,7 @@
         <v>58.3</v>
       </c>
       <c r="S12">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4281,7 +4263,7 @@
         <v>83.3</v>
       </c>
       <c r="S17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4340,7 +4322,7 @@
         <v>96.7</v>
       </c>
       <c r="S18">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4608,7 +4590,7 @@
         <v>88.3</v>
       </c>
       <c r="S23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4726,7 +4708,7 @@
         <v>85</v>
       </c>
       <c r="S25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4785,7 +4767,7 @@
         <v>96.7</v>
       </c>
       <c r="S26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5257,7 +5239,7 @@
         <v>71.7</v>
       </c>
       <c r="S34">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5316,7 +5298,7 @@
         <v>95</v>
       </c>
       <c r="S35">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5523,7 +5505,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5532,16 +5514,16 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>78.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>21.2</v>
+        <v>12.1</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -5555,28 +5537,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="G4" s="2">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5587,7 +5569,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5608,7 +5590,7 @@
         <v>11.8</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5619,28 +5601,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5722,7 +5704,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5754,16 +5736,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22321052600528</v>
+        <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5777,22 +5759,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22321052600528</v>
+        <v>22330051920205</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5800,16 +5782,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920374</v>
+        <v>22321052600528</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5823,22 +5805,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920374</v>
+        <v>22330051920394</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5846,16 +5828,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920002</v>
+        <v>22330051920374</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5864,98 +5846,6 @@
         <v>58</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920205</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920394</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920222</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920224</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20222.xlsx
+++ b/grupos/2ARHV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -222,48 +222,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>ASHLEY</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
   </si>
 </sst>
 </file>
@@ -795,7 +753,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -872,7 +830,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -890,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -949,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>7</v>
@@ -967,7 +925,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1026,7 +984,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1044,7 +1002,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1103,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1180,7 +1138,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1257,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1275,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1334,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1411,7 +1369,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>6</v>
@@ -1488,7 +1446,7 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1506,7 +1464,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1565,7 +1523,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1642,7 +1600,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -1719,7 +1677,7 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>6</v>
@@ -1796,7 +1754,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -1814,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -1873,7 +1831,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -1950,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2027,7 +1985,7 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2086,7 +2044,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2145,7 +2103,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2222,7 +2180,7 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2299,7 +2257,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2376,7 +2334,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>8</v>
@@ -2453,7 +2411,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>8</v>
@@ -2471,7 +2429,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2530,7 +2488,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>8</v>
@@ -2607,7 +2565,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>8</v>
@@ -2684,7 +2642,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -2702,7 +2660,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2761,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -2779,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -2838,7 +2796,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -2915,7 +2873,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -2992,7 +2950,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3069,7 +3027,7 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>6</v>
@@ -3087,7 +3045,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3146,7 +3104,7 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>8</v>
@@ -3223,7 +3181,7 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>9</v>
@@ -3300,7 +3258,7 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>8</v>
@@ -3487,7 +3445,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q4">
         <v>97.8</v>
@@ -3546,7 +3504,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q5">
         <v>86.7</v>
@@ -3605,7 +3563,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3664,7 +3622,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>79.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3723,7 +3681,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3959,7 +3917,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>72.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q12">
         <v>97.8</v>
@@ -4018,7 +3976,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4136,7 +4094,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4195,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>84.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4254,7 +4212,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4372,7 +4330,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4431,7 +4389,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4522,7 +4480,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4581,7 +4539,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4640,7 +4598,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4817,7 +4775,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4876,7 +4834,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -4935,7 +4893,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -4994,7 +4952,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5053,7 +5011,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5112,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5230,7 +5188,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -5289,7 +5247,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -5348,7 +5306,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -5407,7 +5365,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -5473,28 +5431,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>76.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>23.5</v>
+        <v>12.1</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5505,28 +5463,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="G3" s="2">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5704,7 +5662,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5734,121 +5692,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920205</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22321052600528</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920394</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920374</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
